--- a/data/trans_dic/P56$auxiliar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,32 +717,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,05</t>
+          <t>0,0; 53,94</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -752,27 +752,27 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,29</t>
+          <t>0,0; 40,66</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 49,04</t>
+          <t>0,0; 47,21</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,33; 36,34</t>
+          <t>4,38; 35,74</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 77,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 67,24</t>
+          <t>0,0; 65,09</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 30,57</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,02</t>
+          <t>0,0; 39,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0; 44,41</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,02; 49,07</t>
+          <t>5,67; 47,33</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,66</t>
+          <t>0,0; 52,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,52; 34,14</t>
+          <t>5,7; 32,73</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 14,51</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 53,82</t>
+          <t>14,24; 54,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 69,47</t>
+          <t>9,94; 70,44</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18,88; 50,31</t>
+          <t>19,05; 52,3</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,98; 44,01</t>
+          <t>5,91; 42,99</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 9,99</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,6; 45,63</t>
+          <t>21,17; 45,83</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,78</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,88</t>
+          <t>0,0; 16,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,17; 24,02</t>
+          <t>3,24; 26,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13,74; 34,41</t>
+          <t>14,1; 33,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 61,84</t>
+          <t>0,0; 67,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,22</t>
+          <t>0,0; 29,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 37,27</t>
+          <t>0,0; 30,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>18,18; 41,62</t>
+          <t>17,62; 41,57</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,77</t>
+          <t>0,0; 15,83</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,74; 14,45</t>
+          <t>1,72; 14,85</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 20,92</t>
+          <t>1,86; 21,82</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,22; 32,37</t>
+          <t>18,01; 32,82</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>12,22; 59,58</t>
+          <t>11,93; 54,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,07</t>
+          <t>0,0; 21,34</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,48; 42,33</t>
+          <t>10,98; 42,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,22</t>
+          <t>0,0; 31,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 36,49</t>
+          <t>13,77; 36,67</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,18</t>
+          <t>0,0; 17,66</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,87; 36,84</t>
+          <t>22,71; 35,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,65</t>
+          <t>0,0; 15,89</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,85; 37,46</t>
+          <t>17,0; 35,32</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 14,11</t>
+          <t>1,31; 13,3</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,98; 34,42</t>
+          <t>22,2; 34,69</t>
         </is>
       </c>
     </row>
@@ -1432,47 +1432,47 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,86</t>
+          <t>1,89; 17,9</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 27,04</t>
+          <t>12,26; 27,15</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 15,51</t>
+          <t>2,74; 15,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,34; 32,61</t>
+          <t>20,6; 32,96</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 16,86</t>
+          <t>1,89; 17,9</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,07; 27,04</t>
+          <t>12,26; 27,15</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 15,51</t>
+          <t>2,74; 15,38</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>20,13; 32,2</t>
+          <t>19,77; 32,05</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 3,54</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 20,49</t>
+          <t>5,47; 20,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 13,61</t>
+          <t>2,24; 13,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,1; 29,1</t>
+          <t>16,32; 29,82</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>3,15; 13,79</t>
+          <t>2,34; 13,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,39; 26,17</t>
+          <t>14,45; 26,32</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,53; 12,08</t>
+          <t>3,3; 11,99</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,62; 31,07</t>
+          <t>23,37; 31,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,59; 8,99</t>
+          <t>1,64; 10,23</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,48; 22,93</t>
+          <t>13,16; 22,48</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,73; 10,82</t>
+          <t>3,76; 10,4</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,6; 29,53</t>
+          <t>22,48; 29,54</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas</t>
+          <t>Población a la que, al menos, le ayuda los Servicios Sociales cuando tiene dificultades en la actividades básicas (tasa de respuesta: 96,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,32 +1927,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 1007</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1875</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 1982</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3150</t>
+          <t>0; 3087</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 983</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0; 1448</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -1962,27 +1962,27 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2352</t>
+          <t>0; 2373</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 1351</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0; 1977</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5573</t>
+          <t>0; 5365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>501; 4200</t>
+          <t>507; 4131</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 632</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4394</t>
+          <t>0; 4253</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 1483</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3327</t>
+          <t>0; 3430</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0; 1442</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 1475</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 2000</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>488; 3978</t>
+          <t>459; 3837</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 1474</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5092</t>
+          <t>0; 5172</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 1941</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>1100; 5756</t>
+          <t>961; 5518</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 1393</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1649</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0; 1513</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2057; 7381</t>
+          <t>1953; 7411</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 1621</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1046; 7308</t>
+          <t>1046; 7410</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 1920</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3404; 9074</t>
+          <t>3436; 9431</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0; 1641</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1053; 7752</t>
+          <t>1041; 7573</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 1768</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6858; 14488</t>
+          <t>6721; 14551</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 1703</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6750</t>
+          <t>0; 6928</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>782; 5923</t>
+          <t>798; 6613</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6943; 17389</t>
+          <t>7124; 16725</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4548</t>
+          <t>0; 4938</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5504</t>
+          <t>0; 5422</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 8147</t>
+          <t>0; 6604</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5124; 11732</t>
+          <t>4967; 11718</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5807</t>
+          <t>0; 5828</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1060; 8773</t>
+          <t>1047; 9017</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>867; 9731</t>
+          <t>866; 10152</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14343; 25486</t>
+          <t>14180; 25839</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>0; 1607</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2217; 10810</t>
+          <t>2165; 9856</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5666</t>
+          <t>0; 5480</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1902; 7682</t>
+          <t>1993; 7746</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 4181</t>
+          <t>0; 5419</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9636; 23847</t>
+          <t>8996; 23960</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 7577</t>
+          <t>0; 6317</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18943; 30515</t>
+          <t>18815; 29687</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 5405</t>
+          <t>0; 4370</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14905; 31272</t>
+          <t>14193; 29487</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>806; 8667</t>
+          <t>807; 8171</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22193; 34759</t>
+          <t>22415; 35036</t>
         </is>
       </c>
     </row>
@@ -2982,47 +2982,47 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 778</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1080; 10108</t>
+          <t>1135; 10728</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12503; 28015</t>
+          <t>12701; 28135</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2563; 14936</t>
+          <t>2637; 14808</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>20997; 33665</t>
+          <t>21261; 34017</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1080; 10108</t>
+          <t>1135; 10728</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12503; 28015</t>
+          <t>12701; 28135</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2563; 14936</t>
+          <t>2637; 14808</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21214; 33926</t>
+          <t>20831; 33769</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1710</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4144; 16088</t>
+          <t>4292; 16169</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1641; 9814</t>
+          <t>1616; 9403</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15942; 28815</t>
+          <t>16165; 29528</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2942; 12902</t>
+          <t>2188; 12254</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29391; 53464</t>
+          <t>29524; 53761</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6025; 20598</t>
+          <t>5637; 20456</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>58147; 76497</t>
+          <t>57538; 77157</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2256; 12751</t>
+          <t>2331; 14510</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>38107; 64830</t>
+          <t>37209; 63577</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9055; 26259</t>
+          <t>9122; 25237</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>78022; 101954</t>
+          <t>77616; 101981</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P56$auxiliar-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P56$auxiliar-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19,88%</t>
+          <t>19,16%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,65%</t>
         </is>
       </c>
     </row>
@@ -732,7 +732,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 53,94</t>
+          <t>0,0; 52,3</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,66</t>
+          <t>0,0; 45,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,21</t>
+          <t>0,0; 46,96</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>4,38; 35,74</t>
+          <t>0,0; 34,27</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>23,97%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>18,28%</t>
         </is>
       </c>
     </row>
@@ -862,7 +862,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 65,09</t>
+          <t>0,0; 66,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,19</t>
+          <t>0,0; 35,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -892,7 +892,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,67; 47,33</t>
+          <t>6,26; 48,61</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -902,7 +902,7 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,47</t>
+          <t>0,0; 50,15</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -912,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,7; 32,73</t>
+          <t>6,59; 35,35</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>34,33%</t>
+          <t>35,24%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>34,05%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>14,24; 54,04</t>
+          <t>16,59; 54,97</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,94; 70,44</t>
+          <t>10,0; 62,5</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,05; 52,3</t>
+          <t>21,35; 53,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 42,99</t>
+          <t>5,96; 43,73</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -1052,7 +1052,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>21,17; 45,83</t>
+          <t>21,34; 49,0</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>22,2%</t>
+          <t>22,39%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>24,54%</t>
+          <t>25,06%</t>
         </is>
       </c>
     </row>
@@ -1142,17 +1142,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,3</t>
+          <t>0,0; 16,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,24; 26,82</t>
+          <t>3,2; 28,4</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 33,09</t>
+          <t>14,16; 33,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1162,37 +1162,37 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,77</t>
+          <t>0,0; 24,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,21</t>
+          <t>0,0; 36,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>17,62; 41,57</t>
+          <t>19,04; 42,67</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,83</t>
+          <t>0,0; 15,41</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 14,85</t>
+          <t>1,69; 14,42</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,86; 21,82</t>
+          <t>1,87; 21,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18,01; 32,82</t>
+          <t>18,43; 32,85</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>27,97%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>28,08%</t>
+          <t>27,21%</t>
         </is>
       </c>
     </row>
@@ -1282,64 +1282,64 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,93; 54,32</t>
+          <t>12,01; 54,34</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 21,34</t>
+          <t>0,0; 23,12</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,98; 42,68</t>
+          <t>11,16; 41,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,4</t>
+          <t>0,0; 32,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>13,77; 36,67</t>
+          <t>14,9; 36,17</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,66</t>
+          <t>0,0; 18,21</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>22,71; 35,84</t>
+          <t>21,58; 35,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 15,89</t>
+          <t>0,0; 20,25</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>17,0; 35,32</t>
+          <t>17,32; 37,42</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 13,3</t>
+          <t>1,32; 13,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,2; 34,69</t>
+          <t>21,37; 33,42</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,59%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,1%</t>
         </is>
       </c>
     </row>
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 17,9</t>
+          <t>1,83; 16,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12,26; 27,15</t>
+          <t>11,76; 27,34</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 15,38</t>
+          <t>2,72; 15,49</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>20,6; 32,96</t>
+          <t>20,63; 33,18</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 17,9</t>
+          <t>1,83; 16,81</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>12,26; 27,15</t>
+          <t>11,76; 27,34</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,74; 15,38</t>
+          <t>2,72; 15,49</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>19,77; 32,05</t>
+          <t>19,3; 31,5</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,89%</t>
+          <t>25,86%</t>
         </is>
       </c>
     </row>
@@ -1562,57 +1562,57 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>5,47; 20,6</t>
+          <t>4,85; 20,26</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,24; 13,04</t>
+          <t>2,18; 13,04</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>16,32; 29,82</t>
+          <t>16,25; 29,43</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,34; 13,1</t>
+          <t>2,41; 13,87</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,45; 26,32</t>
+          <t>14,71; 26,7</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>3,3; 11,99</t>
+          <t>2,97; 11,93</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23,37; 31,34</t>
+          <t>23,36; 31,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1,64; 10,23</t>
+          <t>1,62; 9,73</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13,16; 22,48</t>
+          <t>13,52; 22,56</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3,76; 10,4</t>
+          <t>3,86; 10,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>22,48; 29,54</t>
+          <t>22,32; 29,45</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1138</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>590</t>
+          <t>669</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1801</t>
         </is>
       </c>
     </row>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 3087</t>
+          <t>0; 3092</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 2373</t>
+          <t>0; 2899</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1977,12 +1977,12 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0; 5365</t>
+          <t>0; 5337</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>507; 4131</t>
+          <t>0; 4214</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1080</t>
+          <t>1083</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>1671</t>
+          <t>2320</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2751</t>
+          <t>3404</t>
         </is>
       </c>
     </row>
@@ -2140,7 +2140,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 4253</t>
+          <t>0; 4364</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -2150,7 +2150,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 3430</t>
+          <t>0; 3165</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2170,7 +2170,7 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>459; 3837</t>
+          <t>606; 4705</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0; 5172</t>
+          <t>0; 4943</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
@@ -2190,7 +2190,7 @@
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>961; 5518</t>
+          <t>1227; 6583</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4288</t>
+          <t>4606</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6191</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>11915</t>
         </is>
       </c>
     </row>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1953; 7411</t>
+          <t>2363; 7833</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1046; 7410</t>
+          <t>1052; 6575</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>3436; 9431</t>
+          <t>4428; 11166</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1041; 7573</t>
+          <t>1050; 7703</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6721; 14551</t>
+          <t>7466; 17146</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>11222</t>
+          <t>12237</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8094</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19316</t>
+          <t>21247</t>
         </is>
       </c>
     </row>
@@ -2556,17 +2556,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 6928</t>
+          <t>0; 7208</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>798; 6613</t>
+          <t>790; 7004</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7124; 16725</t>
+          <t>7739; 18509</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2576,37 +2576,37 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5422</t>
+          <t>0; 4468</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0; 6604</t>
+          <t>0; 7889</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4967; 11718</t>
+          <t>5738; 12858</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0; 5828</t>
+          <t>0; 5672</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1047; 9017</t>
+          <t>1028; 8759</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>866; 10152</t>
+          <t>868; 10161</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>14180; 25839</t>
+          <t>15630; 27851</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4445</t>
+          <t>4422</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>23913</t>
+          <t>25136</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>28359</t>
+          <t>29558</t>
         </is>
       </c>
     </row>
@@ -2764,64 +2764,64 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>2165; 9856</t>
+          <t>2179; 9860</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0; 5480</t>
+          <t>0; 5936</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1993; 7746</t>
+          <t>2095; 7780</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>0; 5419</t>
+          <t>0; 5584</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8996; 23960</t>
+          <t>9736; 23637</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>0; 6317</t>
+          <t>0; 6514</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>18815; 29687</t>
+          <t>19390; 31635</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0; 4370</t>
+          <t>0; 5570</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>14193; 29487</t>
+          <t>14462; 31239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>807; 8171</t>
+          <t>811; 8530</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>22415; 35036</t>
+          <t>23211; 36305</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>28873</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>26767</t>
+          <t>28873</t>
         </is>
       </c>
     </row>
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>1135; 10728</t>
+          <t>1095; 10072</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12701; 28135</t>
+          <t>12183; 28324</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>2637; 14808</t>
+          <t>2624; 14921</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>21261; 34017</t>
+          <t>23283; 37438</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1135; 10728</t>
+          <t>1095; 10072</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>12701; 28135</t>
+          <t>12183; 28324</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>2637; 14808</t>
+          <t>2624; 14921</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>20831; 33769</t>
+          <t>22205; 36239</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>22173</t>
+          <t>23480</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>67227</t>
+          <t>73317</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>89400</t>
+          <t>96798</t>
         </is>
       </c>
     </row>
@@ -3180,57 +3180,57 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>4292; 16169</t>
+          <t>3809; 15906</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1616; 9403</t>
+          <t>1575; 9401</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>16165; 29528</t>
+          <t>17016; 30819</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>2188; 12254</t>
+          <t>2251; 12977</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>29524; 53761</t>
+          <t>30055; 54547</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5637; 20456</t>
+          <t>5072; 20344</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>57538; 77157</t>
+          <t>62998; 84065</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2331; 14510</t>
+          <t>2297; 13806</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>37209; 63577</t>
+          <t>38224; 63781</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>9122; 25237</t>
+          <t>9370; 26025</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>77616; 101981</t>
+          <t>83540; 110246</t>
         </is>
       </c>
     </row>
